--- a/data/Data.xlsx
+++ b/data/Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01-projects\idr-3005_Masteroppgave\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCC8A0A-976B-42CE-AF29-76272ADDCC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24664937-3B95-4A93-964C-13B85698B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="26">
   <si>
     <t>Deltaker</t>
   </si>
@@ -101,6 +101,9 @@
   <si>
     <t>Hb</t>
   </si>
+  <si>
+    <t>Apné tid</t>
+  </si>
 </sst>
 </file>
 
@@ -168,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -185,6 +188,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,10 +469,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EF32"/>
+  <dimension ref="A1:EG32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -874,8 +878,11 @@
       <c r="EF1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="EG1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:137" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1270,7 +1277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
         <v>2</v>
       </c>
@@ -1676,8 +1683,11 @@
       <c r="EF3" s="5">
         <v>17.5</v>
       </c>
+      <c r="EG3" s="8">
+        <v>57.9</v>
+      </c>
     </row>
-    <row r="4" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>4</v>
       </c>
@@ -2083,8 +2093,11 @@
       <c r="EF4" s="5">
         <v>17.5</v>
       </c>
+      <c r="EG4" s="8">
+        <v>28.55</v>
+      </c>
     </row>
-    <row r="5" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>6</v>
       </c>
@@ -2490,8 +2503,11 @@
       <c r="EF5" s="5">
         <v>17.399999999999999</v>
       </c>
+      <c r="EG5" s="8">
+        <v>40.950000000000003</v>
+      </c>
     </row>
-    <row r="6" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>7</v>
       </c>
@@ -2897,8 +2913,11 @@
       <c r="EF6" s="5">
         <v>17</v>
       </c>
+      <c r="EG6" s="8">
+        <v>30.3</v>
+      </c>
     </row>
-    <row r="7" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>8</v>
       </c>
@@ -3304,8 +3323,11 @@
       <c r="EF7" s="5">
         <v>16.850000000000001</v>
       </c>
+      <c r="EG7" s="8">
+        <v>39.94</v>
+      </c>
     </row>
-    <row r="8" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>10</v>
       </c>
@@ -3711,8 +3733,11 @@
       <c r="EF8" s="7">
         <v>16.75</v>
       </c>
+      <c r="EG8" s="8">
+        <v>81.099999999999994</v>
+      </c>
     </row>
-    <row r="9" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>12</v>
       </c>
@@ -4118,8 +4143,11 @@
       <c r="EF9" s="5">
         <v>18.350000000000001</v>
       </c>
+      <c r="EG9" s="8">
+        <v>47.6</v>
+      </c>
     </row>
-    <row r="10" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>13</v>
       </c>
@@ -4525,8 +4553,11 @@
       <c r="EF10" s="5">
         <v>18.450000000000003</v>
       </c>
+      <c r="EG10" s="8">
+        <v>40.83</v>
+      </c>
     </row>
-    <row r="11" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>14</v>
       </c>
@@ -4932,8 +4963,11 @@
       <c r="EF11" s="5">
         <v>15.100000000000001</v>
       </c>
+      <c r="EG11" s="8">
+        <v>43.43</v>
+      </c>
     </row>
-    <row r="12" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>15</v>
       </c>
@@ -5339,8 +5373,11 @@
       <c r="EF12" s="5">
         <v>15.55</v>
       </c>
+      <c r="EG12" s="8">
+        <v>51.99</v>
+      </c>
     </row>
-    <row r="13" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>2</v>
       </c>
@@ -5747,7 +5784,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="14" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>4</v>
       </c>
@@ -6154,7 +6191,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="15" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>6</v>
       </c>
@@ -6561,7 +6598,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="16" spans="1:136" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:137" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>7</v>
       </c>
